--- a/output/cross_ethnic.xlsx
+++ b/output/cross_ethnic.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1104,60 +1104,444 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>NHANES</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>KNHANES (all)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>15138</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2677</v>
+      </c>
+      <c r="P11" t="n">
+        <v>9593</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1319</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cross-cohort</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NHANES</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>KNHANES (all)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>lightGBM</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>15138</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2659</v>
+      </c>
+      <c r="P12" t="n">
+        <v>9598</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1314</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cross-cohort</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NHANES</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>KNHANES (all)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Voting</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>15138</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2646</v>
+      </c>
+      <c r="P13" t="n">
+        <v>9643</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1269</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cross-cohort</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>KNHANES</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>NHANES (all)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CatBoost</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>11660</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.834</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4638</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3927</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2550</v>
+      </c>
+      <c r="R14" t="n">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross-cohort</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>KNHANES</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NHANES (all)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>XGBoost</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E15" t="n">
         <v>11660</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F15" t="n">
         <v>0.86</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G15" t="n">
         <v>0.736</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H15" t="n">
         <v>0.89</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I15" t="n">
         <v>0.613</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J15" t="n">
         <v>0.648</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K15" t="n">
         <v>0.875</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L15" t="n">
         <v>0.75</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M15" t="n">
         <v>0.503</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N15" t="n">
         <v>0.832</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O15" t="n">
         <v>4614</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P15" t="n">
         <v>3971</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q15" t="n">
         <v>2506</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R15" t="n">
         <v>569</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cross-cohort</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>KNHANES</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NHANES (all)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>lightGBM</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>11660</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="O16" t="n">
+        <v>4636</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3908</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2569</v>
+      </c>
+      <c r="R16" t="n">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cross-cohort</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>KNHANES</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NHANES (all)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Voting</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>11660</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4639</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3937</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2540</v>
+      </c>
+      <c r="R17" t="n">
+        <v>544</v>
       </c>
     </row>
   </sheetData>
